--- a/Foundation of Data Analysis/Data-Exploration-Excel/Analysing-Data/Excel-Logic-Functions/Excel-Logic-Functions.xlsx
+++ b/Foundation of Data Analysis/Data-Exploration-Excel/Analysing-Data/Excel-Logic-Functions/Excel-Logic-Functions.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7020"/>
+    <workbookView windowWidth="20490" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,6 +26,38 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+  <si>
+    <t>Project ID</t>
+  </si>
+  <si>
+    <t>Cost Estimation</t>
+  </si>
+  <si>
+    <t>Revenue Estimation</t>
+  </si>
+  <si>
+    <t>Porject result</t>
+  </si>
+  <si>
+    <t>P001</t>
+  </si>
+  <si>
+    <t>P002</t>
+  </si>
+  <si>
+    <t>P003</t>
+  </si>
+  <si>
+    <t>P004</t>
+  </si>
+  <si>
+    <t>P005</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
@@ -34,8 +66,16 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
-    <font>
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -507,139 +547,148 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1166,9 +1215,105 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
-  <sheetData/>
+  <dimension ref="A3:D8"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" customHeight="1" outlineLevelRow="7" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="19.2857142857143" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="19.1428571428571" customWidth="1"/>
+    <col min="4" max="4" width="18.8571428571429" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" customHeight="1" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:4">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3">
+        <v>50000</v>
+      </c>
+      <c r="C4" s="3">
+        <v>75000</v>
+      </c>
+      <c r="D4" t="str">
+        <f>IF(B4&lt;C4,"Profitable project","Failure Project")</f>
+        <v>Profitable project</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="1:4">
+      <c r="A5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3">
+        <v>120000</v>
+      </c>
+      <c r="C5" s="3">
+        <v>100000</v>
+      </c>
+      <c r="D5" t="str">
+        <f>IF(B5&lt;C5,"Profitable project","Failure Project")</f>
+        <v>Failure Project</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:4">
+      <c r="A6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="3">
+        <v>75000</v>
+      </c>
+      <c r="C6" s="3">
+        <v>110000</v>
+      </c>
+      <c r="D6" t="str">
+        <f>IF(B6&lt;C6,"Profitable project","Failure Project")</f>
+        <v>Profitable project</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:4">
+      <c r="A7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="3">
+        <v>200000</v>
+      </c>
+      <c r="C7" s="3">
+        <v>180000</v>
+      </c>
+      <c r="D7" t="str">
+        <f>IF(B7&lt;C7,"Profitable project","Failure Project")</f>
+        <v>Failure Project</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:4">
+      <c r="A8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="3">
+        <v>95000</v>
+      </c>
+      <c r="C8" s="3">
+        <v>140000</v>
+      </c>
+      <c r="D8" t="str">
+        <f>IF(B8&lt;C8,"Profitable project","Failure Project")</f>
+        <v>Profitable project</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
